--- a/clients/elitys/architecture.xlsx
+++ b/clients/elitys/architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theocadene/Documents/IAmi/Documents/clients/elitys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78145138-E7C3-3146-96CF-998DAC42D755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70BE983-2784-1D4F-8494-56DD1B0FC845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="680" windowWidth="29560" windowHeight="19460" xr2:uid="{6AD68B5C-6B0F-9C41-8E15-548C26EF4DF2}"/>
+    <workbookView xWindow="8700" yWindow="680" windowWidth="29560" windowHeight="19460" activeTab="1" xr2:uid="{6AD68B5C-6B0F-9C41-8E15-548C26EF4DF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Service" sheetId="1" r:id="rId1"/>
